--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SERVIGROUP BENIDORM.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SERVIGROUP BENIDORM.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.3109</v>
+        <v>1.2799</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6105</v>
+        <v>1.6835</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2996</v>
+        <v>-0.4036</v>
       </c>
       <c r="G2" t="n">
-        <v>1.0692</v>
+        <v>1.0466</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3335</v>
+        <v>1.3243</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3195</v>
+        <v>2.3637</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9997</v>
+        <v>1.0263</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3198</v>
+        <v>1.3374</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2503</v>
+        <v>-1.3171</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.264</v>
+        <v>-1.3039</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2385</v>
+        <v>-0.2288</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.709</v>
+        <v>-0.6802</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4705</v>
+        <v>0.4514</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8012</v>
+        <v>0.8129</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3098</v>
+        <v>1.4369</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.624</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.0007</v>
+        <v>-2.958</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.5072</v>
+        <v>-1.4717</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4935</v>
+        <v>-1.4864</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.3506</v>
+        <v>-1.2304</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1145</v>
+        <v>-0.023</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.236</v>
+        <v>-1.2074</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6502</v>
+        <v>-1.7276</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3927</v>
+        <v>-1.4487</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2575</v>
+        <v>-0.2789</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S3" t="n">
-        <v>1.802</v>
+        <v>1.7709</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4606</v>
+        <v>1.4462</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3414</v>
+        <v>0.3247</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3103</v>
+        <v>0.3257</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2133</v>
+        <v>3.6279</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.903</v>
+        <v>-3.3022</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7938</v>
+        <v>0.9312</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7957</v>
+        <v>0.9557</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0019</v>
+        <v>-0.0244</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8738</v>
+        <v>3.185</v>
       </c>
       <c r="K4" t="n">
-        <v>2.232</v>
+        <v>2.5122</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6418</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.08</v>
+        <v>-2.2538</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4363</v>
+        <v>-1.5565</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6437</v>
+        <v>-0.6973</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7553</v>
+        <v>0.7387</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1198</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8752</v>
+        <v>0.8227</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.4392</v>
+        <v>-2.5126</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.8988</v>
+        <v>-4.0132</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1167</v>
+        <v>0.1003</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1442</v>
+        <v>1.3652</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0275</v>
+        <v>-1.2649</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5325</v>
+        <v>0.5889</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1735</v>
+        <v>-1.1669</v>
       </c>
       <c r="I5" t="n">
-        <v>1.706</v>
+        <v>1.7558</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3689</v>
+        <v>2.5401</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6834</v>
+        <v>0.7647</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6855</v>
+        <v>1.7754</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8363</v>
+        <v>-1.9512</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8569</v>
+        <v>-1.9316</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0206</v>
+        <v>-0.0197</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4968</v>
+        <v>-0.4822</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2247</v>
+        <v>-1.1749</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7279</v>
+        <v>0.6926</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9196</v>
+        <v>-1.9537</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9196</v>
+        <v>-1.9537</v>
       </c>
     </row>
     <row r="6">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0556</v>
+        <v>0.0508</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2555</v>
+        <v>0.2666</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1998</v>
+        <v>-0.2158</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1912</v>
+        <v>0.1837</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3199</v>
+        <v>0.3284</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3199</v>
+        <v>0.3284</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1287</v>
+        <v>-0.1447</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3999</v>
+        <v>-0.4105</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -922,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1356</v>
+        <v>-0.1329</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0645</v>
+        <v>-0.0618</v>
       </c>
       <c r="U6" t="n">
         <v>-0.0711</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6692</v>
+        <v>-0.6379</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3397</v>
+        <v>-1.1557</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6705</v>
+        <v>0.5179</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2155</v>
+        <v>-1.2255</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3912</v>
+        <v>0.389</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6066</v>
+        <v>-1.6145</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3145</v>
+        <v>-0.2283</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0415</v>
+        <v>1.1008</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.356</v>
+        <v>-1.329</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.901</v>
+        <v>-0.9973</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6503</v>
+        <v>-0.7118</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2506</v>
+        <v>-0.2855</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S7" t="n">
-        <v>1.007</v>
+        <v>0.9829</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7759</v>
+        <v>0.7725</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2311</v>
+        <v>0.2104</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5399</v>
+        <v>1.5521</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3401</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.568</v>
+        <v>-1.5608</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8786</v>
+        <v>-0.7952</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6894</v>
+        <v>-0.7655</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4842</v>
+        <v>-0.5097</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7777</v>
+        <v>-1.7935</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2935</v>
+        <v>1.2837</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7018</v>
+        <v>0.735</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.578</v>
+        <v>-0.5619</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2798</v>
+        <v>1.2968</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1859</v>
+        <v>-1.2447</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1997</v>
+        <v>-1.2316</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4001</v>
+        <v>0.3895</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4837</v>
+        <v>-0.4668</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.5565</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0964</v>
+        <v>0.0897</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7853</v>
+        <v>-1.7701</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9909</v>
+        <v>-2.7854</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2057</v>
+        <v>1.0153</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2642</v>
+        <v>-1.2892</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4155</v>
+        <v>-0.4203</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8486</v>
+        <v>-0.8689</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8343</v>
+        <v>-0.763</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2363</v>
+        <v>-0.1795</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4298</v>
+        <v>-0.5262</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1792</v>
+        <v>-0.2407</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2506</v>
+        <v>-0.2855</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8196</v>
+        <v>0.7975</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3247</v>
+        <v>0.3397</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4949</v>
+        <v>0.4578</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2598</v>
+        <v>0.2795</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5196</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7975</v>
+        <v>-1.7935</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2627</v>
+        <v>-0.0187</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5348</v>
+        <v>-1.7748</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.003</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6377</v>
+        <v>1.6498</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6408</v>
+        <v>-2.5949</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8908</v>
+        <v>1.0851</v>
       </c>
       <c r="K10" t="n">
-        <v>2.881</v>
+        <v>2.9892</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9902</v>
+        <v>-1.9041</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8938</v>
+        <v>-2.0302</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2433</v>
+        <v>-1.3394</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6506</v>
+        <v>-0.6907</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9353</v>
+        <v>-0.9058</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1535</v>
+        <v>-1.1038</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2182</v>
+        <v>0.198</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6909</v>
+        <v>-3.5653</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0644</v>
+        <v>-3.678</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3735</v>
+        <v>0.1126</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.7344</v>
+        <v>-3.6654</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7766</v>
+        <v>-1.7041</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9578</v>
+        <v>-1.9614</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0612</v>
+        <v>-1.8103</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.1182</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9921</v>
+        <v>-1.9286</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6732</v>
+        <v>-1.8551</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.7075</v>
+        <v>-1.8223</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0343</v>
+        <v>-0.0328</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6964</v>
+        <v>-1.6415</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.8626</v>
+        <v>-1.784</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1661</v>
+        <v>0.1425</v>
       </c>
       <c r="V11" t="n">
-        <v>0.7397</v>
+        <v>0.7679</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4775</v>
+        <v>-4.6388</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1032</v>
+        <v>-2.9936</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3743</v>
+        <v>-1.6452</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.7328</v>
+        <v>-4.7895</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.6444</v>
+        <v>-2.6643</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0885</v>
+        <v>-2.1253</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4321</v>
+        <v>-2.3712</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7941</v>
+        <v>-1.7472</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3007</v>
+        <v>-2.4183</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.9171</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4505</v>
+        <v>-1.5013</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4145</v>
+        <v>1.3908</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0094</v>
+        <v>1.0134</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4051</v>
+        <v>0.3774</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1591</v>
+        <v>-1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4789</v>
+        <v>-0.5779</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.3937</v>
+        <v>-11.3968</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.106199999999999</v>
+        <v>-3.046499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.2873</v>
+        <v>-8.350200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.8481</v>
+        <v>-12.632</v>
       </c>
       <c r="H13" t="n">
-        <v>-6.8146</v>
+        <v>-6.586</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.0335</v>
+        <v>-6.0462</v>
       </c>
       <c r="J13" t="n">
-        <v>2.482000000000001</v>
+        <v>3.834099999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>5.3655</v>
+        <v>6.3282</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.8834</v>
+        <v>-2.4941</v>
       </c>
       <c r="M13" t="n">
-        <v>-15.3299</v>
+        <v>-16.4662</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.1801</v>
+        <v>-12.9141</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.15</v>
+        <v>-3.5521</v>
       </c>
       <c r="P13" t="n">
-        <v>3.000800000000001</v>
+        <v>2.921</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.003</v>
+        <v>-9.736799999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>13.0038</v>
+        <v>12.658</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8121</v>
+        <v>1.8228</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.143599999999999</v>
+        <v>-1.8734</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9557</v>
+        <v>3.6961</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.3583</v>
+        <v>-3.5083</v>
       </c>
       <c r="W13" t="n">
-        <v>4.5583</v>
+        <v>4.7296</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.916600000000001</v>
+        <v>-8.2379</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SERVIGROUP BENIDORM.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate_individual/AGG_IND_SERVIGROUP BENIDORM.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.2799</v>
+        <v>1.7065</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6835</v>
+        <v>2.0822</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4036</v>
+        <v>-0.3757</v>
       </c>
       <c r="G2" t="n">
         <v>1.0466</v>
@@ -610,13 +610,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2288</v>
+        <v>0.1977</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6802</v>
+        <v>-0.2815</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4514</v>
+        <v>0.4792</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1221</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. CLOSSET MARTINEZ</t>
+          <t>S. GOMEZ VELEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8129</v>
+        <v>0.3599</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4369</v>
+        <v>1.764</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.624</v>
+        <v>-1.4041</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.958</v>
+        <v>0.5889</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4717</v>
+        <v>-1.1669</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4864</v>
+        <v>1.7558</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.2304</v>
+        <v>2.5401</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.023</v>
+        <v>0.7647</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.2074</v>
+        <v>1.7754</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7276</v>
+        <v>-1.9512</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4487</v>
+        <v>-1.9316</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2789</v>
+        <v>-0.0197</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7789</v>
+        <v>1.9474</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7789</v>
+        <v>1.9474</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7709</v>
+        <v>-0.2226</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4462</v>
+        <v>-0.7762</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3247</v>
+        <v>0.5535</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2211</v>
+        <v>-1.9537</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.9537</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3257</v>
+        <v>0.192</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6279</v>
+        <v>3.5282</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.3022</v>
+        <v>-3.3363</v>
       </c>
       <c r="G4" t="n">
         <v>0.9312</v>
@@ -766,13 +766,13 @@
         <v>2.1421</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7387</v>
+        <v>0.605</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.1836</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8227</v>
+        <v>0.7886</v>
       </c>
       <c r="V4" t="n">
         <v>-2.5126</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. GOMEZ VELEZ</t>
+          <t>R. MARTINEZ BERTOMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1003</v>
+        <v>0.0508</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3652</v>
+        <v>0.2666</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2649</v>
+        <v>-0.2158</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5889</v>
+        <v>0.1837</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1669</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7558</v>
+        <v>0.2658</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5401</v>
+        <v>0.3284</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7647</v>
+        <v>0.3284</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7754</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9512</v>
+        <v>-0.1447</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9316</v>
+        <v>-0.4105</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0197</v>
+        <v>0.2658</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9474</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9474</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4822</v>
+        <v>-0.1329</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1749</v>
+        <v>-0.0618</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6926</v>
+        <v>-0.0711</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.9537</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.9537</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. MARTINEZ BERTOMEU</t>
+          <t>D. CLOSSET MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0508</v>
+        <v>-0.3392</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2666</v>
+        <v>0.3404</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2158</v>
+        <v>-0.6796</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1837</v>
+        <v>-2.958</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-1.4717</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2658</v>
+        <v>-1.4864</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3284</v>
+        <v>-1.2304</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3284</v>
+        <v>-0.023</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.2074</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1447</v>
+        <v>-1.7276</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4105</v>
+        <v>-1.4487</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2658</v>
+        <v>-0.2789</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1329</v>
+        <v>0.6188</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0618</v>
+        <v>0.3498</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0711</v>
+        <v>0.269</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. DESPLACE</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6379</v>
+        <v>-0.4969</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1557</v>
+        <v>0.978</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5179</v>
+        <v>-1.4749</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2255</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.389</v>
+        <v>1.6498</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6145</v>
+        <v>-2.5949</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2283</v>
+        <v>1.0851</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1008</v>
+        <v>2.9892</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.329</v>
+        <v>-1.9041</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9973</v>
+        <v>-2.0302</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7118</v>
+        <v>-1.3394</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2855</v>
+        <v>-0.6907</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.9474</v>
+        <v>1.5579</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.921</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9737</v>
+        <v>1.5579</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9829</v>
+        <v>0.3909</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7725</v>
+        <v>-0.107</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2104</v>
+        <v>0.4979</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5521</v>
+        <v>-1.5005</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3311</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>T. DESPLACE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5608</v>
+        <v>-1.0366</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7952</v>
+        <v>-1.5544</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7655</v>
+        <v>0.5179</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5097</v>
+        <v>-1.2255</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7935</v>
+        <v>0.389</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2837</v>
+        <v>-1.6145</v>
       </c>
       <c r="J8" t="n">
-        <v>0.735</v>
+        <v>-0.2283</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5619</v>
+        <v>1.1008</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2968</v>
+        <v>-1.329</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2447</v>
+        <v>-0.9973</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2316</v>
+        <v>-0.7118</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0131</v>
+        <v>-0.2855</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9737</v>
+        <v>-2.921</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3895</v>
+        <v>0.9737</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4668</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5565</v>
+        <v>0.3738</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0897</v>
+        <v>0.2104</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.5521</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7701</v>
+        <v>-1.2061</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7854</v>
+        <v>-0.4962</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0153</v>
+        <v>-0.7099</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2892</v>
+        <v>-0.5097</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4203</v>
+        <v>-1.7935</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8689</v>
+        <v>1.2837</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.763</v>
+        <v>0.735</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1795</v>
+        <v>-0.5619</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5835</v>
+        <v>1.2968</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5262</v>
+        <v>-1.2447</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2407</v>
+        <v>-1.2316</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2855</v>
+        <v>-0.0131</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.5579</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.921</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3632</v>
+        <v>0.3895</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7975</v>
+        <v>-0.1121</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3397</v>
+        <v>-0.2575</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4578</v>
+        <v>0.1454</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2795</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7935</v>
+        <v>-2.1867</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0187</v>
+        <v>-3.0845</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7748</v>
+        <v>0.8978</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9451000000000001</v>
+        <v>-1.2892</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6498</v>
+        <v>-0.4203</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5949</v>
+        <v>-0.8689</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0851</v>
+        <v>-0.763</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9892</v>
+        <v>-0.1795</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9041</v>
+        <v>-0.5835</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0302</v>
+        <v>-0.5262</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3394</v>
+        <v>-0.2407</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6907</v>
+        <v>-0.2855</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5579</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5579</v>
+        <v>1.3632</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9058</v>
+        <v>0.3809</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1038</v>
+        <v>0.0406</v>
       </c>
       <c r="U10" t="n">
-        <v>0.198</v>
+        <v>0.3403</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5005</v>
+        <v>0.2795</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5005</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5653</v>
+        <v>-2.3451</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.678</v>
+        <v>-2.9802</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1126</v>
+        <v>0.6351</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6654</v>
@@ -1312,13 +1312,13 @@
         <v>1.9474</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6415</v>
+        <v>-0.4213</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.784</v>
+        <v>-1.0863</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1425</v>
+        <v>0.6649</v>
       </c>
       <c r="V11" t="n">
         <v>0.7679</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6388</v>
+        <v>-5.4308</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9936</v>
+        <v>-3.8907</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6452</v>
+        <v>-1.5401</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7895</v>
@@ -1390,13 +1390,13 @@
         <v>0.9737</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3908</v>
+        <v>0.5988</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0134</v>
+        <v>0.1163</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3774</v>
+        <v>0.4824</v>
       </c>
       <c r="V12" t="n">
         <v>-1.24</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.3968</v>
+        <v>-10.7322</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.046499999999999</v>
+        <v>-3.0466</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.350200000000001</v>
+        <v>-7.6856</v>
       </c>
       <c r="G13" t="n">
         <v>-12.632</v>
@@ -1441,10 +1441,10 @@
         <v>-6.0462</v>
       </c>
       <c r="J13" t="n">
-        <v>3.834099999999999</v>
+        <v>3.834100000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>6.3282</v>
+        <v>6.328200000000002</v>
       </c>
       <c r="L13" t="n">
         <v>-2.4941</v>
@@ -1468,16 +1468,16 @@
         <v>12.658</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8228</v>
+        <v>2.4874</v>
       </c>
       <c r="T13" t="n">
         <v>-1.8734</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6961</v>
+        <v>4.3605</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.5083</v>
+        <v>-3.508299999999999</v>
       </c>
       <c r="W13" t="n">
         <v>4.7296</v>
